--- a/ig/DM-OCTOBRE-2024/ValueSet-JDV-J254-CategorieEtablissementESSMSPH.xlsx
+++ b/ig/DM-OCTOBRE-2024/ValueSet-JDV-J254-CategorieEtablissementESSMSPH.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="81">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20231215120000</t>
+    <t>20241025120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-15T12:00:00+01:00</t>
+    <t>2024-10-25T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Liste les catégories d’établissements ESSMS (Etablissement ou Service Social ou Médico-Social) pour les personnes porteurs d’handicap</t>
+    <t>Liste les catégories d'établissements ESSMS (Etablissement ou Service Social ou Médico-Social) pour les personnes porteurs d'handicap</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -177,6 +177,12 @@
     <t>Centre d'Accueil Familial Spécialisé</t>
   </si>
   <si>
+    <t>242</t>
+  </si>
+  <si>
+    <t>Service d'Activité de Jour</t>
+  </si>
+  <si>
     <t>255</t>
   </si>
   <si>
@@ -240,7 +246,7 @@
     <t>640</t>
   </si>
   <si>
-    <t>Service d’aide et d’accompagnement à domicile aux familles (SAADF)</t>
+    <t>Service d'aide et d'accompagnement à domicile aux familles (SAADF)</t>
   </si>
   <si>
     <t/>
@@ -519,7 +525,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -723,15 +729,23 @@
         <v>76</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>78</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
